--- a/presentations/nivel-I/Cronograma_ILUO_Soldadura_Diego_de_Leon.xlsx
+++ b/presentations/nivel-I/Cronograma_ILUO_Soldadura_Diego_de_Leon.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Plan de actividades" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Plan de actividades'!$B$2:$AC$83</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Plan de actividades'!$B$2:$AC$84</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="98">
   <si>
     <t xml:space="preserve">Nombre del proyecto: Certificación ILUO en soldadura robótica GMAW</t>
   </si>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">Documentos de control: WPS, PQR, hoja de parámetros</t>
   </si>
   <si>
-    <t xml:space="preserve">Examen teórico, mínimo 8.0</t>
+    <t xml:space="preserve">Sesión teórica formal y examen 8.0</t>
   </si>
   <si>
     <t xml:space="preserve">Pendiente</t>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t xml:space="preserve">Leyenda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fila Plan: cuándo estaba programada la actividad.  Fila Real: cuándo ocurrió de verdad.</t>
   </si>
   <si>
     <t xml:space="preserve">Plan  ·  y actividad impartida en línea</t>
@@ -628,15 +631,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -676,6 +679,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -702,10 +709,6 @@
     </xf>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -960,7 +963,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:AC82"/>
+  <dimension ref="B2:AC83"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="4.7"/>
@@ -1190,26 +1193,26 @@
       </c>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="14"/>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
-      <c r="AB7" s="14"/>
-      <c r="AC7" s="14"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="15"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="15"/>
+      <c r="AB7" s="15"/>
+      <c r="AC7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="8"/>
@@ -1228,20 +1231,20 @@
       <c r="M8" s="17"/>
       <c r="N8" s="17"/>
       <c r="O8" s="18"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
-      <c r="AB8" s="14"/>
-      <c r="AC8" s="14"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="15"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="15"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="15"/>
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="15"/>
+      <c r="AB8" s="15"/>
+      <c r="AC8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="8" t="n">
@@ -1264,26 +1267,26 @@
       </c>
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="14"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="15"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="15"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="15"/>
+      <c r="Y9" s="15"/>
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="15"/>
+      <c r="AB9" s="15"/>
+      <c r="AC9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8"/>
@@ -1302,20 +1305,20 @@
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
       <c r="O10" s="18"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="14"/>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="14"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
-      <c r="AB10" s="14"/>
-      <c r="AC10" s="14"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="n">
@@ -1338,26 +1341,26 @@
       </c>
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="14"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="14"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="14"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
+      <c r="T11" s="15"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="15"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="15"/>
+      <c r="Y11" s="15"/>
+      <c r="Z11" s="15"/>
+      <c r="AA11" s="15"/>
+      <c r="AB11" s="15"/>
+      <c r="AC11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="8"/>
@@ -1376,20 +1379,20 @@
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
       <c r="O12" s="18"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
-      <c r="S12" s="14"/>
-      <c r="T12" s="14"/>
-      <c r="U12" s="14"/>
-      <c r="V12" s="14"/>
-      <c r="W12" s="14"/>
-      <c r="X12" s="14"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14"/>
-      <c r="AB12" s="14"/>
-      <c r="AC12" s="14"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="15"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="15"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="15"/>
+      <c r="Y12" s="15"/>
+      <c r="Z12" s="15"/>
+      <c r="AA12" s="15"/>
+      <c r="AB12" s="15"/>
+      <c r="AC12" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="n">
@@ -1412,26 +1415,26 @@
       </c>
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="15"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="15"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="15"/>
+      <c r="Y13" s="15"/>
+      <c r="Z13" s="15"/>
+      <c r="AA13" s="15"/>
+      <c r="AB13" s="15"/>
+      <c r="AC13" s="15"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="8"/>
@@ -1450,20 +1453,20 @@
       <c r="M14" s="17"/>
       <c r="N14" s="17"/>
       <c r="O14" s="18"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14"/>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="14"/>
-      <c r="AB14" s="14"/>
-      <c r="AC14" s="14"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="15"/>
+      <c r="U14" s="15"/>
+      <c r="V14" s="15"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="15"/>
+      <c r="Y14" s="15"/>
+      <c r="Z14" s="15"/>
+      <c r="AA14" s="15"/>
+      <c r="AB14" s="15"/>
+      <c r="AC14" s="15"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="8" t="n">
@@ -1486,26 +1489,26 @@
       </c>
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="14"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="15"/>
+      <c r="Y15" s="15"/>
+      <c r="Z15" s="15"/>
+      <c r="AA15" s="15"/>
+      <c r="AB15" s="15"/>
+      <c r="AC15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="8"/>
@@ -1524,20 +1527,20 @@
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
       <c r="O16" s="18"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14"/>
-      <c r="AB16" s="14"/>
-      <c r="AC16" s="14"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="15"/>
+      <c r="T16" s="15"/>
+      <c r="U16" s="15"/>
+      <c r="V16" s="15"/>
+      <c r="W16" s="15"/>
+      <c r="X16" s="15"/>
+      <c r="Y16" s="15"/>
+      <c r="Z16" s="15"/>
+      <c r="AA16" s="15"/>
+      <c r="AB16" s="15"/>
+      <c r="AC16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="8" t="n">
@@ -1560,26 +1563,26 @@
       </c>
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14"/>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="14"/>
-      <c r="AC17" s="14"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
+      <c r="AC17" s="15"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="8"/>
@@ -1598,20 +1601,20 @@
       <c r="M18" s="17"/>
       <c r="N18" s="17"/>
       <c r="O18" s="18"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="14"/>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="14"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14"/>
-      <c r="AB18" s="14"/>
-      <c r="AC18" s="14"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="15"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="15"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="15"/>
+      <c r="Y18" s="15"/>
+      <c r="Z18" s="15"/>
+      <c r="AA18" s="15"/>
+      <c r="AB18" s="15"/>
+      <c r="AC18" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="8" t="n">
@@ -1634,26 +1637,26 @@
       </c>
       <c r="H19" s="14"/>
       <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="14"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
-      <c r="AB19" s="14"/>
-      <c r="AC19" s="14"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15"/>
+      <c r="R19" s="15"/>
+      <c r="S19" s="15"/>
+      <c r="T19" s="15"/>
+      <c r="U19" s="15"/>
+      <c r="V19" s="15"/>
+      <c r="W19" s="15"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="15"/>
+      <c r="Z19" s="15"/>
+      <c r="AA19" s="15"/>
+      <c r="AB19" s="15"/>
+      <c r="AC19" s="15"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="8"/>
@@ -1672,20 +1675,20 @@
       <c r="M20" s="17"/>
       <c r="N20" s="17"/>
       <c r="O20" s="18"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="14"/>
-      <c r="AC20" s="14"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15"/>
+      <c r="S20" s="15"/>
+      <c r="T20" s="15"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="15"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+      <c r="Y20" s="15"/>
+      <c r="Z20" s="15"/>
+      <c r="AA20" s="15"/>
+      <c r="AB20" s="15"/>
+      <c r="AC20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="8" t="n">
@@ -1708,26 +1711,26 @@
       </c>
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="14"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
+      <c r="S21" s="15"/>
+      <c r="T21" s="15"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
+      <c r="Y21" s="15"/>
+      <c r="Z21" s="15"/>
+      <c r="AA21" s="15"/>
+      <c r="AB21" s="15"/>
+      <c r="AC21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="8"/>
@@ -1746,20 +1749,20 @@
       <c r="M22" s="17"/>
       <c r="N22" s="17"/>
       <c r="O22" s="18"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-      <c r="AB22" s="14"/>
-      <c r="AC22" s="14"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
+      <c r="R22" s="15"/>
+      <c r="S22" s="15"/>
+      <c r="T22" s="15"/>
+      <c r="U22" s="15"/>
+      <c r="V22" s="15"/>
+      <c r="W22" s="15"/>
+      <c r="X22" s="15"/>
+      <c r="Y22" s="15"/>
+      <c r="Z22" s="15"/>
+      <c r="AA22" s="15"/>
+      <c r="AB22" s="15"/>
+      <c r="AC22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="8" t="n">
@@ -1782,26 +1785,26 @@
       </c>
       <c r="H23" s="14"/>
       <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
-      <c r="AB23" s="14"/>
-      <c r="AC23" s="14"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="15"/>
+      <c r="T23" s="15"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="15"/>
+      <c r="AA23" s="15"/>
+      <c r="AB23" s="15"/>
+      <c r="AC23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="8"/>
@@ -1820,20 +1823,20 @@
       <c r="M24" s="17"/>
       <c r="N24" s="17"/>
       <c r="O24" s="18"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
-      <c r="AB24" s="14"/>
-      <c r="AC24" s="14"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="15"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
+      <c r="AB24" s="15"/>
+      <c r="AC24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="8" t="n">
@@ -1852,28 +1855,28 @@
       <c r="G25" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
       <c r="S25" s="5"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="14"/>
-      <c r="Z25" s="14"/>
-      <c r="AA25" s="14"/>
-      <c r="AB25" s="14"/>
-      <c r="AC25" s="14"/>
+      <c r="T25" s="15"/>
+      <c r="U25" s="15"/>
+      <c r="V25" s="15"/>
+      <c r="W25" s="15"/>
+      <c r="X25" s="15"/>
+      <c r="Y25" s="15"/>
+      <c r="Z25" s="15"/>
+      <c r="AA25" s="15"/>
+      <c r="AB25" s="15"/>
+      <c r="AC25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="8"/>
@@ -1884,28 +1887,28 @@
       <c r="G26" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-      <c r="X26" s="14"/>
-      <c r="Y26" s="14"/>
-      <c r="Z26" s="14"/>
-      <c r="AA26" s="14"/>
-      <c r="AB26" s="14"/>
-      <c r="AC26" s="14"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+      <c r="S26" s="15"/>
+      <c r="T26" s="15"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="15"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="15"/>
+      <c r="Y26" s="15"/>
+      <c r="Z26" s="15"/>
+      <c r="AA26" s="15"/>
+      <c r="AB26" s="15"/>
+      <c r="AC26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
@@ -1965,21 +1968,21 @@
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
       <c r="N28" s="14"/>
-      <c r="O28" s="15"/>
+      <c r="O28" s="24"/>
       <c r="P28" s="14"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="14"/>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="14"/>
-      <c r="AB28" s="14"/>
-      <c r="AC28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="15"/>
+      <c r="Z28" s="15"/>
+      <c r="AA28" s="15"/>
+      <c r="AB28" s="15"/>
+      <c r="AC28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="8"/>
@@ -1990,28 +1993,28 @@
       <c r="G29" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
       <c r="K29" s="17"/>
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" s="17"/>
       <c r="O29" s="18"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="14"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="14"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="14"/>
-      <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="14"/>
-      <c r="Z29" s="14"/>
-      <c r="AA29" s="14"/>
-      <c r="AB29" s="14"/>
-      <c r="AC29" s="14"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
+      <c r="T29" s="15"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="15"/>
+      <c r="W29" s="15"/>
+      <c r="X29" s="15"/>
+      <c r="Y29" s="15"/>
+      <c r="Z29" s="15"/>
+      <c r="AA29" s="15"/>
+      <c r="AB29" s="15"/>
+      <c r="AC29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="8" t="n">
@@ -2039,21 +2042,21 @@
       <c r="L30" s="14"/>
       <c r="M30" s="14"/>
       <c r="N30" s="14"/>
-      <c r="O30" s="15"/>
+      <c r="O30" s="24"/>
       <c r="P30" s="14"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="14"/>
-      <c r="Z30" s="14"/>
-      <c r="AA30" s="14"/>
-      <c r="AB30" s="14"/>
-      <c r="AC30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="15"/>
+      <c r="Z30" s="15"/>
+      <c r="AA30" s="15"/>
+      <c r="AB30" s="15"/>
+      <c r="AC30" s="15"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="8"/>
@@ -2064,28 +2067,28 @@
       <c r="G31" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
       <c r="K31" s="17"/>
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" s="17"/>
       <c r="O31" s="18"/>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="14"/>
-      <c r="V31" s="14"/>
-      <c r="W31" s="14"/>
-      <c r="X31" s="14"/>
-      <c r="Y31" s="14"/>
-      <c r="Z31" s="14"/>
-      <c r="AA31" s="14"/>
-      <c r="AB31" s="14"/>
-      <c r="AC31" s="14"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="15"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="15"/>
+      <c r="Y31" s="15"/>
+      <c r="Z31" s="15"/>
+      <c r="AA31" s="15"/>
+      <c r="AB31" s="15"/>
+      <c r="AC31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="8" t="n">
@@ -2106,28 +2109,28 @@
       <c r="G32" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
       <c r="O32" s="24"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
-      <c r="V32" s="14"/>
-      <c r="W32" s="14"/>
-      <c r="X32" s="14"/>
-      <c r="Y32" s="14"/>
-      <c r="Z32" s="14"/>
-      <c r="AA32" s="14"/>
-      <c r="AB32" s="14"/>
-      <c r="AC32" s="14"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="15"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="15"/>
+      <c r="W32" s="15"/>
+      <c r="X32" s="15"/>
+      <c r="Y32" s="15"/>
+      <c r="Z32" s="15"/>
+      <c r="AA32" s="15"/>
+      <c r="AB32" s="15"/>
+      <c r="AC32" s="15"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="8"/>
@@ -2138,7 +2141,7 @@
       <c r="G33" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H33" s="14"/>
+      <c r="H33" s="15"/>
       <c r="I33" s="17"/>
       <c r="J33" s="17"/>
       <c r="K33" s="17"/>
@@ -2146,20 +2149,20 @@
       <c r="M33" s="17"/>
       <c r="N33" s="17"/>
       <c r="O33" s="18"/>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
-      <c r="V33" s="14"/>
-      <c r="W33" s="14"/>
-      <c r="X33" s="14"/>
-      <c r="Y33" s="14"/>
-      <c r="Z33" s="14"/>
-      <c r="AA33" s="14"/>
-      <c r="AB33" s="14"/>
-      <c r="AC33" s="14"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="15"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="15"/>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
+      <c r="Y33" s="15"/>
+      <c r="Z33" s="15"/>
+      <c r="AA33" s="15"/>
+      <c r="AB33" s="15"/>
+      <c r="AC33" s="15"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="8" t="n">
@@ -2180,28 +2183,28 @@
       <c r="G34" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="16"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
       <c r="O34" s="24"/>
-      <c r="P34" s="14"/>
-      <c r="Q34" s="14"/>
-      <c r="R34" s="14"/>
-      <c r="S34" s="14"/>
-      <c r="T34" s="14"/>
-      <c r="U34" s="14"/>
-      <c r="V34" s="14"/>
-      <c r="W34" s="14"/>
-      <c r="X34" s="14"/>
-      <c r="Y34" s="14"/>
-      <c r="Z34" s="14"/>
-      <c r="AA34" s="14"/>
-      <c r="AB34" s="14"/>
-      <c r="AC34" s="14"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="15"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="15"/>
+      <c r="W34" s="15"/>
+      <c r="X34" s="15"/>
+      <c r="Y34" s="15"/>
+      <c r="Z34" s="15"/>
+      <c r="AA34" s="15"/>
+      <c r="AB34" s="15"/>
+      <c r="AC34" s="15"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="8"/>
@@ -2212,28 +2215,28 @@
       <c r="G35" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
       <c r="J35" s="17"/>
       <c r="K35" s="17"/>
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" s="17"/>
       <c r="O35" s="18"/>
-      <c r="P35" s="14"/>
-      <c r="Q35" s="14"/>
-      <c r="R35" s="14"/>
-      <c r="S35" s="14"/>
-      <c r="T35" s="14"/>
-      <c r="U35" s="14"/>
-      <c r="V35" s="14"/>
-      <c r="W35" s="14"/>
-      <c r="X35" s="14"/>
-      <c r="Y35" s="14"/>
-      <c r="Z35" s="14"/>
-      <c r="AA35" s="14"/>
-      <c r="AB35" s="14"/>
-      <c r="AC35" s="14"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="15"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="15"/>
+      <c r="T35" s="15"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="15"/>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
+      <c r="Y35" s="15"/>
+      <c r="Z35" s="15"/>
+      <c r="AA35" s="15"/>
+      <c r="AB35" s="15"/>
+      <c r="AC35" s="15"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="8" t="n">
@@ -2254,28 +2257,28 @@
       <c r="G36" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
       <c r="O36" s="24"/>
-      <c r="P36" s="14"/>
-      <c r="Q36" s="14"/>
-      <c r="R36" s="14"/>
-      <c r="S36" s="14"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="14"/>
-      <c r="V36" s="14"/>
-      <c r="W36" s="14"/>
-      <c r="X36" s="14"/>
-      <c r="Y36" s="14"/>
-      <c r="Z36" s="14"/>
-      <c r="AA36" s="14"/>
-      <c r="AB36" s="14"/>
-      <c r="AC36" s="14"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="15"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="15"/>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
+      <c r="Y36" s="15"/>
+      <c r="Z36" s="15"/>
+      <c r="AA36" s="15"/>
+      <c r="AB36" s="15"/>
+      <c r="AC36" s="15"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="8"/>
@@ -2294,20 +2297,20 @@
       <c r="M37" s="17"/>
       <c r="N37" s="17"/>
       <c r="O37" s="18"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="14"/>
-      <c r="AC37" s="14"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="15"/>
+      <c r="R37" s="15"/>
+      <c r="S37" s="15"/>
+      <c r="T37" s="15"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="15"/>
+      <c r="W37" s="15"/>
+      <c r="X37" s="15"/>
+      <c r="Y37" s="15"/>
+      <c r="Z37" s="15"/>
+      <c r="AA37" s="15"/>
+      <c r="AB37" s="15"/>
+      <c r="AC37" s="15"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="8" t="n">
@@ -2326,28 +2329,28 @@
       <c r="G38" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="14"/>
-      <c r="Q38" s="14"/>
-      <c r="R38" s="14"/>
-      <c r="S38" s="14"/>
-      <c r="T38" s="14"/>
-      <c r="U38" s="14"/>
-      <c r="V38" s="14"/>
-      <c r="W38" s="14"/>
-      <c r="X38" s="14"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15"/>
+      <c r="U38" s="15"/>
+      <c r="V38" s="15"/>
+      <c r="W38" s="15"/>
+      <c r="X38" s="15"/>
       <c r="Y38" s="5"/>
-      <c r="Z38" s="14"/>
-      <c r="AA38" s="14"/>
-      <c r="AB38" s="14"/>
-      <c r="AC38" s="14"/>
+      <c r="Z38" s="15"/>
+      <c r="AA38" s="15"/>
+      <c r="AB38" s="15"/>
+      <c r="AC38" s="15"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="8"/>
@@ -2358,28 +2361,28 @@
       <c r="G39" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="14"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="14"/>
-      <c r="Q39" s="14"/>
-      <c r="R39" s="14"/>
-      <c r="S39" s="14"/>
-      <c r="T39" s="14"/>
-      <c r="U39" s="14"/>
-      <c r="V39" s="14"/>
-      <c r="W39" s="14"/>
-      <c r="X39" s="14"/>
-      <c r="Y39" s="14"/>
-      <c r="Z39" s="14"/>
-      <c r="AA39" s="14"/>
-      <c r="AB39" s="14"/>
-      <c r="AC39" s="14"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="15"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="15"/>
+      <c r="T39" s="15"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="15"/>
+      <c r="W39" s="15"/>
+      <c r="X39" s="15"/>
+      <c r="Y39" s="15"/>
+      <c r="Z39" s="15"/>
+      <c r="AA39" s="15"/>
+      <c r="AB39" s="15"/>
+      <c r="AC39" s="15"/>
     </row>
     <row r="40" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
@@ -2432,28 +2435,28 @@
       <c r="G41" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="14"/>
-      <c r="Q41" s="16"/>
-      <c r="R41" s="16"/>
-      <c r="S41" s="16"/>
-      <c r="T41" s="16"/>
-      <c r="U41" s="16"/>
-      <c r="V41" s="16"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="16"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="14"/>
+      <c r="R41" s="14"/>
+      <c r="S41" s="14"/>
+      <c r="T41" s="14"/>
+      <c r="U41" s="14"/>
+      <c r="V41" s="14"/>
       <c r="W41" s="14"/>
       <c r="X41" s="14"/>
       <c r="Y41" s="14"/>
       <c r="Z41" s="14"/>
-      <c r="AA41" s="14"/>
-      <c r="AB41" s="14"/>
-      <c r="AC41" s="14"/>
+      <c r="AA41" s="15"/>
+      <c r="AB41" s="15"/>
+      <c r="AC41" s="15"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="8"/>
@@ -2464,28 +2467,28 @@
       <c r="G42" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
       <c r="M42" s="17"/>
       <c r="N42" s="17"/>
       <c r="O42" s="18"/>
-      <c r="P42" s="14"/>
-      <c r="Q42" s="14"/>
-      <c r="R42" s="14"/>
-      <c r="S42" s="14"/>
-      <c r="T42" s="14"/>
-      <c r="U42" s="14"/>
-      <c r="V42" s="14"/>
-      <c r="W42" s="14"/>
-      <c r="X42" s="14"/>
-      <c r="Y42" s="14"/>
-      <c r="Z42" s="14"/>
-      <c r="AA42" s="14"/>
-      <c r="AB42" s="14"/>
-      <c r="AC42" s="14"/>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="15"/>
+      <c r="R42" s="15"/>
+      <c r="S42" s="15"/>
+      <c r="T42" s="15"/>
+      <c r="U42" s="15"/>
+      <c r="V42" s="15"/>
+      <c r="W42" s="15"/>
+      <c r="X42" s="15"/>
+      <c r="Y42" s="15"/>
+      <c r="Z42" s="15"/>
+      <c r="AA42" s="15"/>
+      <c r="AB42" s="15"/>
+      <c r="AC42" s="15"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="8" t="n">
@@ -2506,28 +2509,28 @@
       <c r="G43" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="14"/>
-      <c r="N43" s="14"/>
-      <c r="O43" s="15"/>
-      <c r="P43" s="14"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="15"/>
+      <c r="N43" s="15"/>
+      <c r="O43" s="16"/>
+      <c r="P43" s="15"/>
       <c r="Q43" s="14"/>
       <c r="R43" s="14"/>
       <c r="S43" s="14"/>
-      <c r="T43" s="16"/>
-      <c r="U43" s="16"/>
-      <c r="V43" s="16"/>
-      <c r="W43" s="16"/>
-      <c r="X43" s="16"/>
-      <c r="Y43" s="16"/>
-      <c r="Z43" s="16"/>
-      <c r="AA43" s="14"/>
-      <c r="AB43" s="14"/>
-      <c r="AC43" s="14"/>
+      <c r="T43" s="14"/>
+      <c r="U43" s="14"/>
+      <c r="V43" s="14"/>
+      <c r="W43" s="14"/>
+      <c r="X43" s="14"/>
+      <c r="Y43" s="14"/>
+      <c r="Z43" s="14"/>
+      <c r="AA43" s="15"/>
+      <c r="AB43" s="15"/>
+      <c r="AC43" s="15"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="8"/>
@@ -2538,28 +2541,28 @@
       <c r="G44" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="14"/>
-      <c r="L44" s="14"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="14"/>
-      <c r="O44" s="15"/>
-      <c r="P44" s="14"/>
-      <c r="Q44" s="14"/>
-      <c r="R44" s="14"/>
-      <c r="S44" s="14"/>
-      <c r="T44" s="14"/>
-      <c r="U44" s="14"/>
-      <c r="V44" s="14"/>
-      <c r="W44" s="14"/>
-      <c r="X44" s="14"/>
-      <c r="Y44" s="14"/>
-      <c r="Z44" s="14"/>
-      <c r="AA44" s="14"/>
-      <c r="AB44" s="14"/>
-      <c r="AC44" s="14"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="15"/>
+      <c r="N44" s="15"/>
+      <c r="O44" s="16"/>
+      <c r="P44" s="15"/>
+      <c r="Q44" s="15"/>
+      <c r="R44" s="15"/>
+      <c r="S44" s="15"/>
+      <c r="T44" s="15"/>
+      <c r="U44" s="15"/>
+      <c r="V44" s="15"/>
+      <c r="W44" s="15"/>
+      <c r="X44" s="15"/>
+      <c r="Y44" s="15"/>
+      <c r="Z44" s="15"/>
+      <c r="AA44" s="15"/>
+      <c r="AB44" s="15"/>
+      <c r="AC44" s="15"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="8" t="n">
@@ -2580,28 +2583,28 @@
       <c r="G45" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
-      <c r="K45" s="14"/>
-      <c r="L45" s="14"/>
-      <c r="M45" s="14"/>
-      <c r="N45" s="14"/>
-      <c r="O45" s="15"/>
-      <c r="P45" s="14"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="15"/>
       <c r="Q45" s="14"/>
       <c r="R45" s="14"/>
       <c r="S45" s="14"/>
-      <c r="T45" s="16"/>
-      <c r="U45" s="16"/>
-      <c r="V45" s="16"/>
-      <c r="W45" s="16"/>
-      <c r="X45" s="16"/>
-      <c r="Y45" s="16"/>
-      <c r="Z45" s="16"/>
-      <c r="AA45" s="14"/>
-      <c r="AB45" s="14"/>
-      <c r="AC45" s="14"/>
+      <c r="T45" s="14"/>
+      <c r="U45" s="14"/>
+      <c r="V45" s="14"/>
+      <c r="W45" s="14"/>
+      <c r="X45" s="14"/>
+      <c r="Y45" s="14"/>
+      <c r="Z45" s="14"/>
+      <c r="AA45" s="15"/>
+      <c r="AB45" s="15"/>
+      <c r="AC45" s="15"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="8"/>
@@ -2612,28 +2615,28 @@
       <c r="G46" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
-      <c r="N46" s="14"/>
-      <c r="O46" s="15"/>
-      <c r="P46" s="14"/>
-      <c r="Q46" s="14"/>
-      <c r="R46" s="14"/>
-      <c r="S46" s="14"/>
-      <c r="T46" s="14"/>
-      <c r="U46" s="14"/>
-      <c r="V46" s="14"/>
-      <c r="W46" s="14"/>
-      <c r="X46" s="14"/>
-      <c r="Y46" s="14"/>
-      <c r="Z46" s="14"/>
-      <c r="AA46" s="14"/>
-      <c r="AB46" s="14"/>
-      <c r="AC46" s="14"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="15"/>
+      <c r="N46" s="15"/>
+      <c r="O46" s="16"/>
+      <c r="P46" s="15"/>
+      <c r="Q46" s="15"/>
+      <c r="R46" s="15"/>
+      <c r="S46" s="15"/>
+      <c r="T46" s="15"/>
+      <c r="U46" s="15"/>
+      <c r="V46" s="15"/>
+      <c r="W46" s="15"/>
+      <c r="X46" s="15"/>
+      <c r="Y46" s="15"/>
+      <c r="Z46" s="15"/>
+      <c r="AA46" s="15"/>
+      <c r="AB46" s="15"/>
+      <c r="AC46" s="15"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="8" t="n">
@@ -2652,28 +2655,28 @@
       <c r="G47" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="14"/>
-      <c r="L47" s="14"/>
-      <c r="M47" s="14"/>
-      <c r="N47" s="14"/>
-      <c r="O47" s="15"/>
-      <c r="P47" s="14"/>
-      <c r="Q47" s="14"/>
-      <c r="R47" s="14"/>
-      <c r="S47" s="14"/>
-      <c r="T47" s="14"/>
-      <c r="U47" s="14"/>
-      <c r="V47" s="14"/>
-      <c r="W47" s="14"/>
-      <c r="X47" s="14"/>
-      <c r="Y47" s="14"/>
-      <c r="Z47" s="14"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="16"/>
+      <c r="P47" s="15"/>
+      <c r="Q47" s="15"/>
+      <c r="R47" s="15"/>
+      <c r="S47" s="15"/>
+      <c r="T47" s="15"/>
+      <c r="U47" s="15"/>
+      <c r="V47" s="15"/>
+      <c r="W47" s="15"/>
+      <c r="X47" s="15"/>
+      <c r="Y47" s="15"/>
+      <c r="Z47" s="15"/>
       <c r="AA47" s="5"/>
-      <c r="AB47" s="14"/>
-      <c r="AC47" s="14"/>
+      <c r="AB47" s="15"/>
+      <c r="AC47" s="15"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="8"/>
@@ -2684,28 +2687,28 @@
       <c r="G48" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="15"/>
-      <c r="P48" s="14"/>
-      <c r="Q48" s="14"/>
-      <c r="R48" s="14"/>
-      <c r="S48" s="14"/>
-      <c r="T48" s="14"/>
-      <c r="U48" s="14"/>
-      <c r="V48" s="14"/>
-      <c r="W48" s="14"/>
-      <c r="X48" s="14"/>
-      <c r="Y48" s="14"/>
-      <c r="Z48" s="14"/>
-      <c r="AA48" s="14"/>
-      <c r="AB48" s="14"/>
-      <c r="AC48" s="14"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="15"/>
+      <c r="Q48" s="15"/>
+      <c r="R48" s="15"/>
+      <c r="S48" s="15"/>
+      <c r="T48" s="15"/>
+      <c r="U48" s="15"/>
+      <c r="V48" s="15"/>
+      <c r="W48" s="15"/>
+      <c r="X48" s="15"/>
+      <c r="Y48" s="15"/>
+      <c r="Z48" s="15"/>
+      <c r="AA48" s="15"/>
+      <c r="AB48" s="15"/>
+      <c r="AC48" s="15"/>
     </row>
     <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="5" t="s">
@@ -2758,28 +2761,28 @@
       <c r="G50" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="14"/>
-      <c r="Q50" s="14"/>
-      <c r="R50" s="14"/>
-      <c r="S50" s="14"/>
-      <c r="T50" s="14"/>
-      <c r="U50" s="14"/>
-      <c r="V50" s="14"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="16"/>
+      <c r="P50" s="15"/>
+      <c r="Q50" s="15"/>
+      <c r="R50" s="15"/>
+      <c r="S50" s="15"/>
+      <c r="T50" s="15"/>
+      <c r="U50" s="15"/>
+      <c r="V50" s="15"/>
       <c r="W50" s="14"/>
       <c r="X50" s="14"/>
       <c r="Y50" s="14"/>
       <c r="Z50" s="14"/>
-      <c r="AA50" s="16"/>
-      <c r="AB50" s="16"/>
-      <c r="AC50" s="16"/>
+      <c r="AA50" s="14"/>
+      <c r="AB50" s="14"/>
+      <c r="AC50" s="14"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="8"/>
@@ -2790,28 +2793,28 @@
       <c r="G51" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="14"/>
-      <c r="Q51" s="14"/>
-      <c r="R51" s="14"/>
-      <c r="S51" s="14"/>
-      <c r="T51" s="14"/>
-      <c r="U51" s="14"/>
-      <c r="V51" s="14"/>
-      <c r="W51" s="14"/>
-      <c r="X51" s="14"/>
-      <c r="Y51" s="14"/>
-      <c r="Z51" s="14"/>
-      <c r="AA51" s="14"/>
-      <c r="AB51" s="14"/>
-      <c r="AC51" s="14"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="15"/>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15"/>
+      <c r="O51" s="16"/>
+      <c r="P51" s="15"/>
+      <c r="Q51" s="15"/>
+      <c r="R51" s="15"/>
+      <c r="S51" s="15"/>
+      <c r="T51" s="15"/>
+      <c r="U51" s="15"/>
+      <c r="V51" s="15"/>
+      <c r="W51" s="15"/>
+      <c r="X51" s="15"/>
+      <c r="Y51" s="15"/>
+      <c r="Z51" s="15"/>
+      <c r="AA51" s="15"/>
+      <c r="AB51" s="15"/>
+      <c r="AC51" s="15"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="8" t="n">
@@ -2832,28 +2835,28 @@
       <c r="G52" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
-      <c r="N52" s="14"/>
-      <c r="O52" s="15"/>
-      <c r="P52" s="14"/>
-      <c r="Q52" s="14"/>
-      <c r="R52" s="14"/>
-      <c r="S52" s="14"/>
-      <c r="T52" s="14"/>
-      <c r="U52" s="14"/>
-      <c r="V52" s="14"/>
-      <c r="W52" s="16"/>
-      <c r="X52" s="16"/>
-      <c r="Y52" s="16"/>
-      <c r="Z52" s="16"/>
-      <c r="AA52" s="16"/>
-      <c r="AB52" s="16"/>
-      <c r="AC52" s="14"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="15"/>
+      <c r="M52" s="15"/>
+      <c r="N52" s="15"/>
+      <c r="O52" s="16"/>
+      <c r="P52" s="15"/>
+      <c r="Q52" s="15"/>
+      <c r="R52" s="15"/>
+      <c r="S52" s="15"/>
+      <c r="T52" s="15"/>
+      <c r="U52" s="15"/>
+      <c r="V52" s="15"/>
+      <c r="W52" s="14"/>
+      <c r="X52" s="14"/>
+      <c r="Y52" s="14"/>
+      <c r="Z52" s="14"/>
+      <c r="AA52" s="14"/>
+      <c r="AB52" s="14"/>
+      <c r="AC52" s="15"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="8"/>
@@ -2864,28 +2867,28 @@
       <c r="G53" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="14"/>
-      <c r="O53" s="15"/>
-      <c r="P53" s="14"/>
-      <c r="Q53" s="14"/>
-      <c r="R53" s="14"/>
-      <c r="S53" s="14"/>
-      <c r="T53" s="14"/>
-      <c r="U53" s="14"/>
-      <c r="V53" s="14"/>
-      <c r="W53" s="14"/>
-      <c r="X53" s="14"/>
-      <c r="Y53" s="14"/>
-      <c r="Z53" s="14"/>
-      <c r="AA53" s="14"/>
-      <c r="AB53" s="14"/>
-      <c r="AC53" s="14"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="15"/>
+      <c r="M53" s="15"/>
+      <c r="N53" s="15"/>
+      <c r="O53" s="16"/>
+      <c r="P53" s="15"/>
+      <c r="Q53" s="15"/>
+      <c r="R53" s="15"/>
+      <c r="S53" s="15"/>
+      <c r="T53" s="15"/>
+      <c r="U53" s="15"/>
+      <c r="V53" s="15"/>
+      <c r="W53" s="15"/>
+      <c r="X53" s="15"/>
+      <c r="Y53" s="15"/>
+      <c r="Z53" s="15"/>
+      <c r="AA53" s="15"/>
+      <c r="AB53" s="15"/>
+      <c r="AC53" s="15"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="8" t="n">
@@ -2906,27 +2909,27 @@
       <c r="G54" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-      <c r="N54" s="14"/>
-      <c r="O54" s="15"/>
-      <c r="P54" s="14"/>
-      <c r="Q54" s="14"/>
-      <c r="R54" s="14"/>
-      <c r="S54" s="14"/>
-      <c r="T54" s="14"/>
-      <c r="U54" s="14"/>
-      <c r="V54" s="14"/>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
+      <c r="L54" s="15"/>
+      <c r="M54" s="15"/>
+      <c r="N54" s="15"/>
+      <c r="O54" s="16"/>
+      <c r="P54" s="15"/>
+      <c r="Q54" s="15"/>
+      <c r="R54" s="15"/>
+      <c r="S54" s="15"/>
+      <c r="T54" s="15"/>
+      <c r="U54" s="15"/>
+      <c r="V54" s="15"/>
       <c r="W54" s="14"/>
       <c r="X54" s="14"/>
-      <c r="Y54" s="16"/>
-      <c r="Z54" s="16"/>
-      <c r="AA54" s="16"/>
-      <c r="AB54" s="16"/>
+      <c r="Y54" s="14"/>
+      <c r="Z54" s="14"/>
+      <c r="AA54" s="14"/>
+      <c r="AB54" s="14"/>
       <c r="AC54" s="14"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2938,28 +2941,28 @@
       <c r="G55" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-      <c r="M55" s="14"/>
-      <c r="N55" s="14"/>
-      <c r="O55" s="15"/>
-      <c r="P55" s="14"/>
-      <c r="Q55" s="14"/>
-      <c r="R55" s="14"/>
-      <c r="S55" s="14"/>
-      <c r="T55" s="14"/>
-      <c r="U55" s="14"/>
-      <c r="V55" s="14"/>
-      <c r="W55" s="14"/>
-      <c r="X55" s="14"/>
-      <c r="Y55" s="14"/>
-      <c r="Z55" s="14"/>
-      <c r="AA55" s="14"/>
-      <c r="AB55" s="14"/>
-      <c r="AC55" s="14"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="15"/>
+      <c r="M55" s="15"/>
+      <c r="N55" s="15"/>
+      <c r="O55" s="16"/>
+      <c r="P55" s="15"/>
+      <c r="Q55" s="15"/>
+      <c r="R55" s="15"/>
+      <c r="S55" s="15"/>
+      <c r="T55" s="15"/>
+      <c r="U55" s="15"/>
+      <c r="V55" s="15"/>
+      <c r="W55" s="15"/>
+      <c r="X55" s="15"/>
+      <c r="Y55" s="15"/>
+      <c r="Z55" s="15"/>
+      <c r="AA55" s="15"/>
+      <c r="AB55" s="15"/>
+      <c r="AC55" s="15"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="8" t="n">
@@ -2980,27 +2983,27 @@
       <c r="G56" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
-      <c r="N56" s="14"/>
-      <c r="O56" s="15"/>
-      <c r="P56" s="14"/>
-      <c r="Q56" s="14"/>
-      <c r="R56" s="14"/>
-      <c r="S56" s="14"/>
-      <c r="T56" s="14"/>
-      <c r="U56" s="14"/>
-      <c r="V56" s="14"/>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="15"/>
+      <c r="M56" s="15"/>
+      <c r="N56" s="15"/>
+      <c r="O56" s="16"/>
+      <c r="P56" s="15"/>
+      <c r="Q56" s="15"/>
+      <c r="R56" s="15"/>
+      <c r="S56" s="15"/>
+      <c r="T56" s="15"/>
+      <c r="U56" s="15"/>
+      <c r="V56" s="15"/>
       <c r="W56" s="14"/>
       <c r="X56" s="14"/>
-      <c r="Y56" s="16"/>
-      <c r="Z56" s="16"/>
-      <c r="AA56" s="16"/>
-      <c r="AB56" s="16"/>
+      <c r="Y56" s="14"/>
+      <c r="Z56" s="14"/>
+      <c r="AA56" s="14"/>
+      <c r="AB56" s="14"/>
       <c r="AC56" s="14"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3012,28 +3015,28 @@
       <c r="G57" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="14"/>
-      <c r="N57" s="14"/>
-      <c r="O57" s="15"/>
-      <c r="P57" s="14"/>
-      <c r="Q57" s="14"/>
-      <c r="R57" s="14"/>
-      <c r="S57" s="14"/>
-      <c r="T57" s="14"/>
-      <c r="U57" s="14"/>
-      <c r="V57" s="14"/>
-      <c r="W57" s="14"/>
-      <c r="X57" s="14"/>
-      <c r="Y57" s="14"/>
-      <c r="Z57" s="14"/>
-      <c r="AA57" s="14"/>
-      <c r="AB57" s="14"/>
-      <c r="AC57" s="14"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="15"/>
+      <c r="M57" s="15"/>
+      <c r="N57" s="15"/>
+      <c r="O57" s="16"/>
+      <c r="P57" s="15"/>
+      <c r="Q57" s="15"/>
+      <c r="R57" s="15"/>
+      <c r="S57" s="15"/>
+      <c r="T57" s="15"/>
+      <c r="U57" s="15"/>
+      <c r="V57" s="15"/>
+      <c r="W57" s="15"/>
+      <c r="X57" s="15"/>
+      <c r="Y57" s="15"/>
+      <c r="Z57" s="15"/>
+      <c r="AA57" s="15"/>
+      <c r="AB57" s="15"/>
+      <c r="AC57" s="15"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="8" t="n">
@@ -3054,28 +3057,28 @@
       <c r="G58" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H58" s="16"/>
-      <c r="I58" s="16"/>
-      <c r="J58" s="16"/>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="16"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
+      <c r="M58" s="14"/>
+      <c r="N58" s="14"/>
       <c r="O58" s="24"/>
-      <c r="P58" s="16"/>
-      <c r="Q58" s="16"/>
-      <c r="R58" s="16"/>
-      <c r="S58" s="16"/>
-      <c r="T58" s="16"/>
-      <c r="U58" s="16"/>
-      <c r="V58" s="16"/>
-      <c r="W58" s="16"/>
-      <c r="X58" s="16"/>
-      <c r="Y58" s="16"/>
-      <c r="Z58" s="16"/>
-      <c r="AA58" s="16"/>
-      <c r="AB58" s="16"/>
-      <c r="AC58" s="16"/>
+      <c r="P58" s="14"/>
+      <c r="Q58" s="14"/>
+      <c r="R58" s="14"/>
+      <c r="S58" s="14"/>
+      <c r="T58" s="14"/>
+      <c r="U58" s="14"/>
+      <c r="V58" s="14"/>
+      <c r="W58" s="14"/>
+      <c r="X58" s="14"/>
+      <c r="Y58" s="14"/>
+      <c r="Z58" s="14"/>
+      <c r="AA58" s="14"/>
+      <c r="AB58" s="14"/>
+      <c r="AC58" s="14"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="8"/>
@@ -3086,7 +3089,7 @@
       <c r="G59" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H59" s="14"/>
+      <c r="H59" s="17"/>
       <c r="I59" s="17"/>
       <c r="J59" s="17"/>
       <c r="K59" s="17"/>
@@ -3094,20 +3097,20 @@
       <c r="M59" s="17"/>
       <c r="N59" s="17"/>
       <c r="O59" s="18"/>
-      <c r="P59" s="14"/>
-      <c r="Q59" s="14"/>
-      <c r="R59" s="14"/>
-      <c r="S59" s="14"/>
-      <c r="T59" s="14"/>
-      <c r="U59" s="14"/>
-      <c r="V59" s="14"/>
-      <c r="W59" s="14"/>
-      <c r="X59" s="14"/>
-      <c r="Y59" s="14"/>
-      <c r="Z59" s="14"/>
-      <c r="AA59" s="14"/>
-      <c r="AB59" s="14"/>
-      <c r="AC59" s="14"/>
+      <c r="P59" s="15"/>
+      <c r="Q59" s="15"/>
+      <c r="R59" s="15"/>
+      <c r="S59" s="15"/>
+      <c r="T59" s="15"/>
+      <c r="U59" s="15"/>
+      <c r="V59" s="15"/>
+      <c r="W59" s="15"/>
+      <c r="X59" s="15"/>
+      <c r="Y59" s="15"/>
+      <c r="Z59" s="15"/>
+      <c r="AA59" s="15"/>
+      <c r="AB59" s="15"/>
+      <c r="AC59" s="15"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B60" s="8" t="n">
@@ -3128,27 +3131,27 @@
       <c r="G60" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-      <c r="N60" s="14"/>
-      <c r="O60" s="15"/>
-      <c r="P60" s="14"/>
-      <c r="Q60" s="14"/>
-      <c r="R60" s="14"/>
-      <c r="S60" s="14"/>
-      <c r="T60" s="14"/>
-      <c r="U60" s="14"/>
-      <c r="V60" s="14"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="16"/>
+      <c r="P60" s="15"/>
+      <c r="Q60" s="15"/>
+      <c r="R60" s="15"/>
+      <c r="S60" s="15"/>
+      <c r="T60" s="15"/>
+      <c r="U60" s="15"/>
+      <c r="V60" s="15"/>
       <c r="W60" s="14"/>
       <c r="X60" s="14"/>
-      <c r="Y60" s="16"/>
-      <c r="Z60" s="16"/>
-      <c r="AA60" s="16"/>
-      <c r="AB60" s="16"/>
+      <c r="Y60" s="14"/>
+      <c r="Z60" s="14"/>
+      <c r="AA60" s="14"/>
+      <c r="AB60" s="14"/>
       <c r="AC60" s="14"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3160,28 +3163,28 @@
       <c r="G61" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="14"/>
-      <c r="O61" s="15"/>
-      <c r="P61" s="14"/>
-      <c r="Q61" s="14"/>
-      <c r="R61" s="14"/>
-      <c r="S61" s="14"/>
-      <c r="T61" s="14"/>
-      <c r="U61" s="14"/>
-      <c r="V61" s="14"/>
-      <c r="W61" s="14"/>
-      <c r="X61" s="14"/>
-      <c r="Y61" s="14"/>
-      <c r="Z61" s="14"/>
-      <c r="AA61" s="14"/>
-      <c r="AB61" s="14"/>
-      <c r="AC61" s="14"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="15"/>
+      <c r="M61" s="15"/>
+      <c r="N61" s="15"/>
+      <c r="O61" s="16"/>
+      <c r="P61" s="15"/>
+      <c r="Q61" s="15"/>
+      <c r="R61" s="15"/>
+      <c r="S61" s="15"/>
+      <c r="T61" s="15"/>
+      <c r="U61" s="15"/>
+      <c r="V61" s="15"/>
+      <c r="W61" s="15"/>
+      <c r="X61" s="15"/>
+      <c r="Y61" s="15"/>
+      <c r="Z61" s="15"/>
+      <c r="AA61" s="15"/>
+      <c r="AB61" s="15"/>
+      <c r="AC61" s="15"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B62" s="8" t="n">
@@ -3200,27 +3203,27 @@
       <c r="G62" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="14"/>
-      <c r="O62" s="15"/>
-      <c r="P62" s="14"/>
-      <c r="Q62" s="14"/>
-      <c r="R62" s="14"/>
-      <c r="S62" s="14"/>
-      <c r="T62" s="14"/>
-      <c r="U62" s="14"/>
-      <c r="V62" s="14"/>
-      <c r="W62" s="14"/>
-      <c r="X62" s="14"/>
-      <c r="Y62" s="14"/>
-      <c r="Z62" s="14"/>
-      <c r="AA62" s="14"/>
-      <c r="AB62" s="14"/>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="15"/>
+      <c r="M62" s="15"/>
+      <c r="N62" s="15"/>
+      <c r="O62" s="16"/>
+      <c r="P62" s="15"/>
+      <c r="Q62" s="15"/>
+      <c r="R62" s="15"/>
+      <c r="S62" s="15"/>
+      <c r="T62" s="15"/>
+      <c r="U62" s="15"/>
+      <c r="V62" s="15"/>
+      <c r="W62" s="15"/>
+      <c r="X62" s="15"/>
+      <c r="Y62" s="15"/>
+      <c r="Z62" s="15"/>
+      <c r="AA62" s="15"/>
+      <c r="AB62" s="15"/>
       <c r="AC62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3232,28 +3235,28 @@
       <c r="G63" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
-      <c r="N63" s="14"/>
-      <c r="O63" s="15"/>
-      <c r="P63" s="14"/>
-      <c r="Q63" s="14"/>
-      <c r="R63" s="14"/>
-      <c r="S63" s="14"/>
-      <c r="T63" s="14"/>
-      <c r="U63" s="14"/>
-      <c r="V63" s="14"/>
-      <c r="W63" s="14"/>
-      <c r="X63" s="14"/>
-      <c r="Y63" s="14"/>
-      <c r="Z63" s="14"/>
-      <c r="AA63" s="14"/>
-      <c r="AB63" s="14"/>
-      <c r="AC63" s="14"/>
+      <c r="H63" s="15"/>
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="15"/>
+      <c r="M63" s="15"/>
+      <c r="N63" s="15"/>
+      <c r="O63" s="16"/>
+      <c r="P63" s="15"/>
+      <c r="Q63" s="15"/>
+      <c r="R63" s="15"/>
+      <c r="S63" s="15"/>
+      <c r="T63" s="15"/>
+      <c r="U63" s="15"/>
+      <c r="V63" s="15"/>
+      <c r="W63" s="15"/>
+      <c r="X63" s="15"/>
+      <c r="Y63" s="15"/>
+      <c r="Z63" s="15"/>
+      <c r="AA63" s="15"/>
+      <c r="AB63" s="15"/>
+      <c r="AC63" s="15"/>
     </row>
     <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B64" s="5" t="s">
@@ -3306,28 +3309,28 @@
       <c r="G65" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H65" s="16"/>
-      <c r="I65" s="16"/>
-      <c r="J65" s="16"/>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="16"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="14"/>
+      <c r="L65" s="14"/>
+      <c r="M65" s="14"/>
+      <c r="N65" s="14"/>
       <c r="O65" s="24"/>
-      <c r="P65" s="16"/>
-      <c r="Q65" s="16"/>
-      <c r="R65" s="16"/>
-      <c r="S65" s="16"/>
-      <c r="T65" s="16"/>
-      <c r="U65" s="16"/>
-      <c r="V65" s="16"/>
-      <c r="W65" s="16"/>
-      <c r="X65" s="16"/>
-      <c r="Y65" s="14"/>
-      <c r="Z65" s="14"/>
-      <c r="AA65" s="14"/>
-      <c r="AB65" s="14"/>
-      <c r="AC65" s="14"/>
+      <c r="P65" s="14"/>
+      <c r="Q65" s="14"/>
+      <c r="R65" s="14"/>
+      <c r="S65" s="14"/>
+      <c r="T65" s="14"/>
+      <c r="U65" s="14"/>
+      <c r="V65" s="14"/>
+      <c r="W65" s="14"/>
+      <c r="X65" s="14"/>
+      <c r="Y65" s="15"/>
+      <c r="Z65" s="15"/>
+      <c r="AA65" s="15"/>
+      <c r="AB65" s="15"/>
+      <c r="AC65" s="15"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="8"/>
@@ -3346,20 +3349,20 @@
       <c r="M66" s="17"/>
       <c r="N66" s="17"/>
       <c r="O66" s="18"/>
-      <c r="P66" s="14"/>
-      <c r="Q66" s="14"/>
-      <c r="R66" s="14"/>
-      <c r="S66" s="14"/>
-      <c r="T66" s="14"/>
-      <c r="U66" s="14"/>
-      <c r="V66" s="14"/>
-      <c r="W66" s="14"/>
-      <c r="X66" s="14"/>
-      <c r="Y66" s="14"/>
-      <c r="Z66" s="14"/>
-      <c r="AA66" s="14"/>
-      <c r="AB66" s="14"/>
-      <c r="AC66" s="14"/>
+      <c r="P66" s="15"/>
+      <c r="Q66" s="15"/>
+      <c r="R66" s="15"/>
+      <c r="S66" s="15"/>
+      <c r="T66" s="15"/>
+      <c r="U66" s="15"/>
+      <c r="V66" s="15"/>
+      <c r="W66" s="15"/>
+      <c r="X66" s="15"/>
+      <c r="Y66" s="15"/>
+      <c r="Z66" s="15"/>
+      <c r="AA66" s="15"/>
+      <c r="AB66" s="15"/>
+      <c r="AC66" s="15"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C68" s="25" t="s">
@@ -3367,159 +3370,164 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="16"/>
       <c r="C69" s="26" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="17"/>
-      <c r="C70" s="26" t="s">
+      <c r="B70" s="14"/>
+      <c r="C70" s="27" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="27"/>
-      <c r="C71" s="26" t="s">
+      <c r="B71" s="17"/>
+      <c r="C71" s="27" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="5"/>
-      <c r="C72" s="26" t="s">
+      <c r="B72" s="28"/>
+      <c r="C72" s="27" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C74" s="25" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="5"/>
+      <c r="C73" s="27" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C75" s="28" t="s">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C75" s="25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C76" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="D75" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="E75" s="28" t="s">
+      <c r="D76" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="E76" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="F75" s="28" t="s">
+      <c r="F76" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="G75" s="28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C76" s="29" t="s">
+      <c r="G76" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D76" s="30" t="n">
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C77" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D77" s="31" t="n">
         <f aca="false">COUNTIF(D6:D66,"I")</f>
         <v>9</v>
       </c>
-      <c r="E76" s="30" t="n">
+      <c r="E77" s="31" t="n">
         <f aca="false">COUNTIFS(D6:D66,"I",E6:E66,"Dominado")</f>
         <v>0</v>
       </c>
-      <c r="F76" s="30" t="n">
+      <c r="F77" s="31" t="n">
         <f aca="false">COUNTIFS(D6:D66,"I",E6:E66,"Parcial")</f>
         <v>9</v>
       </c>
-      <c r="G76" s="30" t="n">
+      <c r="G77" s="31" t="n">
         <f aca="false">COUNTIFS(D6:D66,"I",E6:E66,"No iniciado")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C77" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="D77" s="30" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C78" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D78" s="31" t="n">
         <f aca="false">COUNTIF(D6:D66,"L")</f>
         <v>5</v>
       </c>
-      <c r="E77" s="30" t="n">
+      <c r="E78" s="31" t="n">
         <f aca="false">COUNTIFS(D6:D66,"L",E6:E66,"Dominado")</f>
         <v>3</v>
       </c>
-      <c r="F77" s="30" t="n">
+      <c r="F78" s="31" t="n">
         <f aca="false">COUNTIFS(D6:D66,"L",E6:E66,"Parcial")</f>
         <v>2</v>
       </c>
-      <c r="G77" s="30" t="n">
+      <c r="G78" s="31" t="n">
         <f aca="false">COUNTIFS(D6:D66,"L",E6:E66,"No iniciado")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C78" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="D78" s="30" t="n">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C79" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D79" s="31" t="n">
         <f aca="false">COUNTIF(D6:D66,"U")</f>
         <v>3</v>
       </c>
-      <c r="E78" s="30" t="n">
+      <c r="E79" s="31" t="n">
         <f aca="false">COUNTIFS(D6:D66,"U",E6:E66,"Dominado")</f>
         <v>0</v>
       </c>
-      <c r="F78" s="30" t="n">
+      <c r="F79" s="31" t="n">
         <f aca="false">COUNTIFS(D6:D66,"U",E6:E66,"Parcial")</f>
         <v>1</v>
       </c>
-      <c r="G78" s="30" t="n">
+      <c r="G79" s="31" t="n">
         <f aca="false">COUNTIFS(D6:D66,"U",E6:E66,"No iniciado")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C79" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D79" s="30" t="n">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C80" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="D80" s="31" t="n">
         <f aca="false">COUNTIF(D6:D66,"O")</f>
         <v>6</v>
       </c>
-      <c r="E79" s="30" t="n">
+      <c r="E80" s="31" t="n">
         <f aca="false">COUNTIFS(D6:D66,"O",E6:E66,"Dominado")</f>
         <v>1</v>
       </c>
-      <c r="F79" s="30" t="n">
+      <c r="F80" s="31" t="n">
         <f aca="false">COUNTIFS(D6:D66,"O",E6:E66,"Parcial")</f>
         <v>0</v>
       </c>
-      <c r="G79" s="30" t="n">
+      <c r="G80" s="31" t="n">
         <f aca="false">COUNTIFS(D6:D66,"O",E6:E66,"No iniciado")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C80" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D80" s="32" t="n">
-        <f aca="false">SUM(D76:D79)</f>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C81" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="D81" s="33" t="n">
+        <f aca="false">SUM(D77:D80)</f>
         <v>23</v>
       </c>
-      <c r="E80" s="32" t="n">
-        <f aca="false">SUM(E76:E79)</f>
+      <c r="E81" s="33" t="n">
+        <f aca="false">SUM(E77:E80)</f>
         <v>4</v>
       </c>
-      <c r="F80" s="32" t="n">
-        <f aca="false">SUM(F76:F79)</f>
+      <c r="F81" s="33" t="n">
+        <f aca="false">SUM(F77:F80)</f>
         <v>12</v>
       </c>
-      <c r="G80" s="32" t="n">
-        <f aca="false">SUM(G76:G79)</f>
+      <c r="G81" s="33" t="n">
+        <f aca="false">SUM(G77:G80)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C82" s="33" t="s">
-        <v>96</v>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C83" s="26" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
